--- a/marketing_surveys/022_men_s_hair_styling_product_usage_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/022_men_s_hair_styling_product_usage_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'less_than_1_time_a_week'}</t>
+          <t>less_than_1_time_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Less than 1 time a week'}</t>
+          <t>Less than 1 time a week</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1_time_a_week'}</t>
+          <t>1_time_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1 time a week'}</t>
+          <t>1 time a week</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2-3_times_a_week'}</t>
+          <t>2-3_times_a_week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2-3 times a week'}</t>
+          <t>2-3 times a week</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'clean_shaven'}</t>
+          <t>clean_shaven</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Clean shaven'}</t>
+          <t>Clean shaven</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'light_hold'}</t>
+          <t>light_hold</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Light hold'}</t>
+          <t>Light hold</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'medium_hold'}</t>
+          <t>medium_hold</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Medium hold'}</t>
+          <t>Medium hold</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'heavy_hold'}</t>
+          <t>heavy_hold</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Heavy hold'}</t>
+          <t>Heavy hold</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Straight'}</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'curly'}</t>
+          <t>curly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Curly'}</t>
+          <t>Curly</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'wavy'}</t>
+          <t>wavy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Wavy'}</t>
+          <t>Wavy</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'in-app'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'In-app'}</t>
+          <t>In-app</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'thick'}</t>
+          <t>thick</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Thick'}</t>
+          <t>Thick</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'thin'}</t>
+          <t>thin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Thin'}</t>
+          <t>Thin</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Blonde'}</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'oval'}</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Oval'}</t>
+          <t>Oval</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'round'}</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Round'}</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'heart'}</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Heart'}</t>
+          <t>Heart</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'square'}</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Square'}</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'little'}</t>
+          <t>little</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Little'}</t>
+          <t>Little</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'less_than_1_time_a_week'}</t>
+          <t>less_than_1_time_a_week</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Less than 1 time a week'}</t>
+          <t>Less than 1 time a week</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1_time_a_week'}</t>
+          <t>1_time_a_week</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1 time a week'}</t>
+          <t>1 time a week</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2-3_times_a_week'}</t>
+          <t>2-3_times_a_week</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2-3 times a week'}</t>
+          <t>2-3 times a week</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'less_than_1_time_a_week'}</t>
+          <t>less_than_1_time_a_week</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Less than 1 time a week'}</t>
+          <t>Less than 1 time a week</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1_time_a_week'}</t>
+          <t>1_time_a_week</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1 time a week'}</t>
+          <t>1 time a week</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2-3_times_a_week'}</t>
+          <t>2-3_times_a_week</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2-3 times a week'}</t>
+          <t>2-3 times a week</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'less_than_1_time_a_week'}</t>
+          <t>less_than_1_time_a_week</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Less than 1 time a week'}</t>
+          <t>Less than 1 time a week</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1_time_a_week'}</t>
+          <t>1_time_a_week</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1 time a week'}</t>
+          <t>1 time a week</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2-3_times_a_week'}</t>
+          <t>2-3_times_a_week</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2-3 times a week'}</t>
+          <t>2-3 times a week</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
